--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Vital Signs, ResourceType Observation, Variation Flow</t>
+    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -1759,10 +1759,10 @@
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
+    <t>1239: source value from GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
+  </si>
+  <si>
     <t>Vital.VitalSign.SupplementalO2</t>
-  </si>
-  <si>
-    <t>1239: source value from GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component.value[x]:valueQuantity.comparator</t>
@@ -2394,8 +2394,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="102.74609375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="102.74609375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationFlow.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
